--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_MOOSE_COW.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_MOOSE_COW.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -668,8 +674,13 @@
           <t>37.5</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -736,8 +747,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -804,8 +820,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
